--- a/03_김현우_Ensemble/artifacts/submissions/HUFS_validation_avgrate.xlsx
+++ b/03_김현우_Ensemble/artifacts/submissions/HUFS_validation_avgrate.xlsx
@@ -440,10 +440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19459</v>
+        <v>19459.39487639445</v>
       </c>
       <c r="C2" t="n">
-        <v>5.405277777777778</v>
+        <v>5.405387465665126</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29361</v>
+        <v>29361.35853063026</v>
       </c>
       <c r="C3" t="n">
-        <v>8.155833333333334</v>
+        <v>8.155932925175071</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36626</v>
+        <v>36626.41258625122</v>
       </c>
       <c r="C4" t="n">
-        <v>10.17388888888889</v>
+        <v>10.17400349618089</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36201</v>
+        <v>36201.13173108891</v>
       </c>
       <c r="C5" t="n">
-        <v>10.05583333333333</v>
+        <v>10.05586992530248</v>
       </c>
     </row>
     <row r="6">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1310</v>
+        <v>1310.033202873141</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3638888888888889</v>
+        <v>0.363898111909206</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48506</v>
+        <v>48505.5758981559</v>
       </c>
       <c r="C7" t="n">
-        <v>13.47388888888889</v>
+        <v>13.47377108282108</v>
       </c>
     </row>
   </sheetData>
